--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135494391</v>
+        <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>852813</v>
+        <v>852439</v>
       </c>
       <c r="R6" t="n">
-        <v>7375454</v>
+        <v>7375368</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1197,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,27 +1227,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494391</t>
+          <t>https://artportalen.se/Sighting/136948349</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135494392</v>
+        <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>852798</v>
+        <v>852657</v>
       </c>
       <c r="R7" t="n">
-        <v>7375455</v>
+        <v>7375266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,27 +1309,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>gammal fruktkropp, ny fruktkropp och vit mycelmatta</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,31 +1333,30 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494392</t>
+          <t>https://artportalen.se/Sighting/136948345</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135494394</v>
+        <v>135494391</v>
       </c>
       <c r="B8" t="n">
         <v>93363</v>
@@ -1400,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>852754</v>
+        <v>852813</v>
       </c>
       <c r="R8" t="n">
-        <v>7375447</v>
+        <v>7375454</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,13 +1462,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494394</t>
+          <t>https://artportalen.se/Sighting/135494391</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135494395</v>
+        <v>135494392</v>
       </c>
       <c r="B9" t="n">
         <v>93363</v>
@@ -1506,19 +1497,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>852741</v>
+        <v>852798</v>
       </c>
       <c r="R9" t="n">
-        <v>7375423</v>
+        <v>7375455</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1551,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp, ny fruktkropp och vit mycelmatta</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,6 +1565,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1583,13 +1583,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494395</t>
+          <t>https://artportalen.se/Sighting/135494392</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135494396</v>
+        <v>135494394</v>
       </c>
       <c r="B10" t="n">
         <v>93363</v>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>852725</v>
+        <v>852754</v>
       </c>
       <c r="R10" t="n">
-        <v>7375423</v>
+        <v>7375447</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,13 +1695,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494396</t>
+          <t>https://artportalen.se/Sighting/135494394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135494397</v>
+        <v>135494395</v>
       </c>
       <c r="B11" t="n">
         <v>93363</v>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>852740</v>
+        <v>852741</v>
       </c>
       <c r="R11" t="n">
-        <v>7375427</v>
+        <v>7375423</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,13 +1807,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494397</t>
+          <t>https://artportalen.se/Sighting/135494395</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135494401</v>
+        <v>135494396</v>
       </c>
       <c r="B12" t="n">
         <v>93363</v>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>852726</v>
+        <v>852725</v>
       </c>
       <c r="R12" t="n">
-        <v>7375386</v>
+        <v>7375423</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,13 +1919,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494401</t>
+          <t>https://artportalen.se/Sighting/135494396</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135494403</v>
+        <v>135494397</v>
       </c>
       <c r="B13" t="n">
         <v>93363</v>
@@ -1954,22 +1954,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>852695</v>
+        <v>852740</v>
       </c>
       <c r="R13" t="n">
-        <v>7375400</v>
+        <v>7375427</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>vit mycelmatta</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,7 +2014,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,13 +2031,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494403</t>
+          <t>https://artportalen.se/Sighting/135494397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135494404</v>
+        <v>135494401</v>
       </c>
       <c r="B14" t="n">
         <v>93363</v>
@@ -2081,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>852689</v>
+        <v>852726</v>
       </c>
       <c r="R14" t="n">
-        <v>7375444</v>
+        <v>7375386</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,13 +2143,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494404</t>
+          <t>https://artportalen.se/Sighting/135494401</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135494415</v>
+        <v>135494403</v>
       </c>
       <c r="B15" t="n">
         <v>93363</v>
@@ -2187,16 +2178,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>852553</v>
+        <v>852695</v>
       </c>
       <c r="R15" t="n">
-        <v>7375372</v>
+        <v>7375400</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2232,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>vit mycelmatta</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,6 +2246,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2264,13 +2264,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494415</t>
+          <t>https://artportalen.se/Sighting/135494403</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135494416</v>
+        <v>135494404</v>
       </c>
       <c r="B16" t="n">
         <v>93363</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>852528</v>
+        <v>852689</v>
       </c>
       <c r="R16" t="n">
-        <v>7375354</v>
+        <v>7375444</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,13 +2376,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494416</t>
+          <t>https://artportalen.se/Sighting/135494404</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135494419</v>
+        <v>135494415</v>
       </c>
       <c r="B17" t="n">
         <v>93363</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>852478</v>
+        <v>852553</v>
       </c>
       <c r="R17" t="n">
-        <v>7375365</v>
+        <v>7375372</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,13 +2488,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494419</t>
+          <t>https://artportalen.se/Sighting/135494415</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135494424</v>
+        <v>135494416</v>
       </c>
       <c r="B18" t="n">
         <v>93363</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>852350</v>
+        <v>852528</v>
       </c>
       <c r="R18" t="n">
-        <v>7375294</v>
+        <v>7375354</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,13 +2600,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494424</t>
+          <t>https://artportalen.se/Sighting/135494416</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135494426</v>
+        <v>135494419</v>
       </c>
       <c r="B19" t="n">
         <v>93363</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>852406</v>
+        <v>852478</v>
       </c>
       <c r="R19" t="n">
-        <v>7375258</v>
+        <v>7375365</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,13 +2712,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494426</t>
+          <t>https://artportalen.se/Sighting/135494419</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135522433</v>
+        <v>135494424</v>
       </c>
       <c r="B20" t="n">
         <v>93363</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>852655</v>
+        <v>852350</v>
       </c>
       <c r="R20" t="n">
-        <v>7375384</v>
+        <v>7375294</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,24 +2813,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522433</t>
+          <t>https://artportalen.se/Sighting/135494424</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135522436</v>
+        <v>135494426</v>
       </c>
       <c r="B21" t="n">
         <v>93363</v>
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>852432</v>
+        <v>852406</v>
       </c>
       <c r="R21" t="n">
-        <v>7375242</v>
+        <v>7375258</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,24 +2925,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522436</t>
+          <t>https://artportalen.se/Sighting/135494426</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135522437</v>
+        <v>135522433</v>
       </c>
       <c r="B22" t="n">
         <v>93363</v>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>852414</v>
+        <v>852655</v>
       </c>
       <c r="R22" t="n">
-        <v>7375232</v>
+        <v>7375384</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,16 +3048,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522437</t>
+          <t>https://artportalen.se/Sighting/135522433</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135522430</v>
+        <v>135522436</v>
       </c>
       <c r="B23" t="n">
-        <v>93375</v>
+        <v>93363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>852692</v>
+        <v>852432</v>
       </c>
       <c r="R23" t="n">
-        <v>7375409</v>
+        <v>7375242</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,16 +3160,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522430</t>
+          <t>https://artportalen.se/Sighting/135522436</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135494410</v>
+        <v>135522437</v>
       </c>
       <c r="B24" t="n">
-        <v>93007</v>
+        <v>93363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3201,13 +3201,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>852758</v>
+        <v>852414</v>
       </c>
       <c r="R24" t="n">
-        <v>7375446</v>
+        <v>7375232</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,27 +3261,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494410</t>
+          <t>https://artportalen.se/Sighting/135522437</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135494418</v>
+        <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93007</v>
+        <v>93411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3313,13 +3313,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>852497</v>
+        <v>852667</v>
       </c>
       <c r="R25" t="n">
-        <v>7375353</v>
+        <v>7375282</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3343,22 +3343,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,49 +3373,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494418</t>
+          <t>https://artportalen.se/Sighting/136948343</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135494398</v>
+        <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>93411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>852747</v>
+        <v>852482</v>
       </c>
       <c r="R26" t="n">
-        <v>7375401</v>
+        <v>7375276</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,22 +3455,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,49 +3485,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494398</t>
+          <t>https://artportalen.se/Sighting/136948348</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135494417</v>
+        <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>93411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>852504</v>
+        <v>852499</v>
       </c>
       <c r="R27" t="n">
-        <v>7375347</v>
+        <v>7375394</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,22 +3567,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,68 +3597,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494417</t>
+          <t>https://artportalen.se/Sighting/136948350</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135495703</v>
+        <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Garnlav, Nb</t>
+          <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>852805</v>
+        <v>852538</v>
       </c>
       <c r="R28" t="n">
-        <v>7375392</v>
+        <v>7375399</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3682,12 +3679,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,56 +3703,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495703</t>
+          <t>https://artportalen.se/Sighting/136948353</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135522434</v>
+        <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>93411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3755,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>852417</v>
+        <v>852678</v>
       </c>
       <c r="R29" t="n">
-        <v>7375334</v>
+        <v>7375384</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,22 +3791,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,44 +3826,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522434</t>
+          <t>https://artportalen.se/Sighting/136948354</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135494402</v>
+        <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>79468</v>
+        <v>93411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3867,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>852696</v>
+        <v>852689</v>
       </c>
       <c r="R30" t="n">
-        <v>7375404</v>
+        <v>7375395</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3897,22 +3903,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,49 +3933,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494402</t>
+          <t>https://artportalen.se/Sighting/136948355</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135494411</v>
+        <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>79468</v>
+        <v>93411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3979,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>852712</v>
+        <v>852776</v>
       </c>
       <c r="R31" t="n">
-        <v>7375445</v>
+        <v>7375393</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4009,22 +4015,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,49 +4045,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494411</t>
+          <t>https://artportalen.se/Sighting/136948356</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135494422</v>
+        <v>135522430</v>
       </c>
       <c r="B32" t="n">
-        <v>79468</v>
+        <v>93375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4091,13 +4097,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>852344</v>
+        <v>852692</v>
       </c>
       <c r="R32" t="n">
-        <v>7375306</v>
+        <v>7375409</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4126,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4136,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,49 +4157,49 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494422</t>
+          <t>https://artportalen.se/Sighting/135522430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135522427</v>
+        <v>135494410</v>
       </c>
       <c r="B33" t="n">
-        <v>79468</v>
+        <v>93007</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4203,13 +4209,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>852717</v>
+        <v>852758</v>
       </c>
       <c r="R33" t="n">
-        <v>7375373</v>
+        <v>7375446</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4238,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4248,7 +4254,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,27 +4269,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522427</t>
+          <t>https://artportalen.se/Sighting/135494410</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135494423</v>
+        <v>135494418</v>
       </c>
       <c r="B34" t="n">
-        <v>79201</v>
+        <v>93007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4291,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4315,13 +4321,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>852336</v>
+        <v>852497</v>
       </c>
       <c r="R34" t="n">
-        <v>7375305</v>
+        <v>7375353</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4350,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,7 +4366,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,59 +4392,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494423</t>
+          <t>https://artportalen.se/Sighting/135494418</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136044719</v>
+        <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>57193</v>
+        <v>90707</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>4962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>852790</v>
+        <v>852667</v>
       </c>
       <c r="R35" t="n">
-        <v>7375455</v>
+        <v>7375285</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4462,12 +4463,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4482,27 +4493,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136044719</t>
+          <t>https://artportalen.se/Sighting/136948342</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136063599</v>
+        <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>58167</v>
+        <v>93437</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,37 +4521,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Garnlav, Nb</t>
+          <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>852805</v>
+        <v>852904</v>
       </c>
       <c r="R36" t="n">
-        <v>7375392</v>
+        <v>7375430</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4564,12 +4575,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4584,49 +4605,49 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136063599</t>
+          <t>https://artportalen.se/Sighting/136948360</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135494400</v>
+        <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>98162</v>
+        <v>93449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4636,13 +4657,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>852756</v>
+        <v>852799</v>
       </c>
       <c r="R37" t="n">
-        <v>7375386</v>
+        <v>7375410</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4666,22 +4687,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4696,27 +4717,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494400</t>
+          <t>https://artportalen.se/Sighting/136948357</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135494393</v>
+        <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>79467</v>
+        <v>93449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4724,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4748,13 +4769,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>852762</v>
+        <v>852852</v>
       </c>
       <c r="R38" t="n">
-        <v>7375449</v>
+        <v>7375436</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4778,22 +4799,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,27 +4829,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494393</t>
+          <t>https://artportalen.se/Sighting/136948358</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135494399</v>
+        <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>79467</v>
+        <v>93449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,21 +4857,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>260591</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4860,13 +4881,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>852765</v>
+        <v>852904</v>
       </c>
       <c r="R39" t="n">
-        <v>7375381</v>
+        <v>7375430</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4890,22 +4911,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4920,49 +4941,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494399</t>
+          <t>https://artportalen.se/Sighting/136948359</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135494412</v>
+        <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>79467</v>
+        <v>90895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>260591</v>
+        <v>6286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4972,13 +4993,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>852548</v>
+        <v>852573</v>
       </c>
       <c r="R40" t="n">
-        <v>7375432</v>
+        <v>7375260</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5002,22 +5023,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,49 +5053,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494412</t>
+          <t>https://artportalen.se/Sighting/136948346</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135494413</v>
+        <v>135494398</v>
       </c>
       <c r="B41" t="n">
-        <v>79467</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5084,13 +5105,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>852548</v>
+        <v>852747</v>
       </c>
       <c r="R41" t="n">
-        <v>7375398</v>
+        <v>7375401</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5119,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5129,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,38 +5176,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494413</t>
+          <t>https://artportalen.se/Sighting/135494398</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135494421</v>
+        <v>135494417</v>
       </c>
       <c r="B42" t="n">
-        <v>79467</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5196,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>852355</v>
+        <v>852504</v>
       </c>
       <c r="R42" t="n">
-        <v>7375316</v>
+        <v>7375347</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,54 +5288,57 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494421</t>
+          <t>https://artportalen.se/Sighting/135494417</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135522428</v>
+        <v>135495703</v>
       </c>
       <c r="B43" t="n">
-        <v>79467</v>
+        <v>79445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vislakt, Nb</t>
+          <t>Garnlav, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>852717</v>
+        <v>852805</v>
       </c>
       <c r="R43" t="n">
-        <v>7375373</v>
+        <v>7375392</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5341,76 +5365,67 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522428</t>
+          <t>https://artportalen.se/Sighting/135495703</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135522429</v>
+        <v>135522434</v>
       </c>
       <c r="B44" t="n">
-        <v>79467</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5420,13 +5435,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>852707</v>
+        <v>852417</v>
       </c>
       <c r="R44" t="n">
-        <v>7375383</v>
+        <v>7375334</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,7 +5470,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5465,7 +5480,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,38 +5506,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522429</t>
+          <t>https://artportalen.se/Sighting/135522434</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135522431</v>
+        <v>135494402</v>
       </c>
       <c r="B45" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>260591</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5532,13 +5547,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>852686</v>
+        <v>852696</v>
       </c>
       <c r="R45" t="n">
-        <v>7375375</v>
+        <v>7375404</v>
       </c>
       <c r="S45" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5592,49 +5607,49 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522431</t>
+          <t>https://artportalen.se/Sighting/135494402</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135522432</v>
+        <v>135494411</v>
       </c>
       <c r="B46" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>260591</v>
+        <v>6434</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5644,13 +5659,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>852674</v>
+        <v>852712</v>
       </c>
       <c r="R46" t="n">
-        <v>7375369</v>
+        <v>7375445</v>
       </c>
       <c r="S46" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5679,7 +5694,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5689,7 +5704,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5704,16 +5719,2027 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494411</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135494422</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79468</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>852344</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7375306</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494422</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135522427</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79468</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>852717</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7375373</v>
+      </c>
+      <c r="S48" t="n">
+        <v>12</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522427</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136948340</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>852726</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7375340</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136948340</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135494423</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>852336</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7375305</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494423</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136948339</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>852774</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7375295</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136948338</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>852494</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7375411</v>
+      </c>
+      <c r="S52" t="n">
+        <v>41</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136948338</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136044719</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57193</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>852790</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7375455</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136044719</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136063599</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Garnlav, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>852805</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7375392</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136063599</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135494400</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98162</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>852756</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7375386</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494400</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135494393</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>852762</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7375449</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494393</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135494399</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>852765</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7375381</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494399</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135494412</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7375432</v>
+      </c>
+      <c r="S58" t="n">
+        <v>7</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494412</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135494413</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7375398</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494413</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135494421</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>852355</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7375316</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494421</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135522428</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>852717</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7375373</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522428</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135522429</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>852707</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7375383</v>
+      </c>
+      <c r="S62" t="n">
+        <v>12</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522429</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135522431</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>852686</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7375375</v>
+      </c>
+      <c r="S63" t="n">
+        <v>32</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522431</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135522432</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>852674</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7375369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>19</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135522432</t>
         </is>
@@ -5766,6 +7792,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6325,11 +6325,7 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90776</v>
+        <v>90777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80654</v>
+        <v>80655</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 63242-2025 artfynd.xlsx
+++ b/artfynd/A 63242-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136948349</v>
       </c>
       <c r="B6" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136948345</v>
       </c>
       <c r="B7" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136948343</v>
       </c>
       <c r="B25" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136948348</v>
       </c>
       <c r="B26" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>136948350</v>
       </c>
       <c r="B27" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>136948353</v>
       </c>
       <c r="B28" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>136948354</v>
       </c>
       <c r="B29" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>136948355</v>
       </c>
       <c r="B30" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136948356</v>
       </c>
       <c r="B31" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>136948342</v>
       </c>
       <c r="B35" t="n">
-        <v>90777</v>
+        <v>90780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>136948360</v>
       </c>
       <c r="B36" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136948357</v>
       </c>
       <c r="B37" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136948358</v>
       </c>
       <c r="B38" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>136948359</v>
       </c>
       <c r="B39" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>136948346</v>
       </c>
       <c r="B40" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136948340</v>
       </c>
       <c r="B49" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>136948339</v>
       </c>
       <c r="B51" t="n">
-        <v>80655</v>
+        <v>80658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136948338</v>
       </c>
       <c r="B52" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
